--- a/その他/ゲーム展示会/会場.xlsx
+++ b/その他/ゲーム展示会/会場.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_araki\Documents\授業資料\Textbook\その他\ゲーム展示会\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC46ACA-925F-477F-AD2A-0F17F30B7210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F28372-DFF7-4255-AFEA-13E9471CB095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{014623EE-1EA6-4F77-A9E6-360ABCF67025}"/>
   </bookViews>
   <sheets>
-    <sheet name="受付" sheetId="6" r:id="rId1"/>
-    <sheet name="164" sheetId="3" r:id="rId2"/>
-    <sheet name="174" sheetId="4" r:id="rId3"/>
-    <sheet name="173" sheetId="5" r:id="rId4"/>
+    <sheet name="164" sheetId="3" r:id="rId1"/>
+    <sheet name="174" sheetId="4" r:id="rId2"/>
+    <sheet name="173" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -488,21 +487,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -510,33 +536,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
@@ -882,107 +881,97 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B89EE5-5290-4FB0-AEFC-3719280D0B70}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26258CF2-8E5A-4980-9622-6FC324DDFB3B}">
   <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="E1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="B1" s="7"/>
+      <c r="E1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="17"/>
-      <c r="B2" s="18"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="14"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="17"/>
-      <c r="B3" s="18"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="9"/>
     </row>
     <row r="4" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="19"/>
-      <c r="B4" s="20"/>
-      <c r="E4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="8" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="E4" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E5" s="5"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="9"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="9" t="s">
+      <c r="E6" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="E7" s="12"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="E8" s="2"/>
@@ -993,53 +982,53 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="8" t="s">
+      <c r="E9" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E10" s="5"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="9"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="18" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="E12" s="12"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="E13" s="2"/>
@@ -1063,17 +1052,17 @@
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="11"/>
+      <c r="B16" s="20"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="I16" s="11"/>
+      <c r="I16" s="20"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="2"/>
@@ -1081,6 +1070,23 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="I9:I10"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="E1:E2"/>
@@ -1092,23 +1098,219 @@
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
-    <mergeCell ref="I6:I7"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E51BAC-0A7E-4C75-9569-C9646E721574}">
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="E1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9"/>
+    </row>
+    <row r="4" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="E4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E7" s="13"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E9" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E10" s="16"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="28"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E11" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="23"/>
+    </row>
+    <row r="12" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E12" s="10"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="20"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="H16:I16"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="E11:I12"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:I10"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1117,97 +1319,92 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E51BAC-0A7E-4C75-9569-C9646E721574}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{164A49E5-759C-4953-83FC-053B5969CFD0}">
   <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="E1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>5</v>
-      </c>
+      <c r="I1" s="7"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="17"/>
-      <c r="B2" s="18"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="14"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="9"/>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="17"/>
-      <c r="B3" s="18"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="9"/>
     </row>
     <row r="4" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="19"/>
-      <c r="B4" s="20"/>
-      <c r="E4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>5</v>
-      </c>
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="11"/>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E5" s="5"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="9"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>5</v>
-      </c>
+      <c r="A6" s="8"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="E7" s="12"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="E8" s="2"/>
@@ -1218,45 +1415,51 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="27" t="s">
-        <v>5</v>
-      </c>
+      <c r="A9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E10" s="5"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="28"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E11" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="23"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="E12" s="19"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="20"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="E13" s="2"/>
@@ -1280,231 +1483,17 @@
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" s="11"/>
+      <c r="A16" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="20"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="E11:I12"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{164A49E5-759C-4953-83FC-053B5969CFD0}">
-  <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A1" s="15"/>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="19"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18"/>
-    </row>
-    <row r="4" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" s="17"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" s="17"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="19"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A9" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A10" s="17"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A11" s="17"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="19"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="10" t="s">
+      <c r="H16" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="11"/>
+      <c r="I16" s="20"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="2"/>
